--- a/output/graficos_dimensiones/comunal_i_ingr_a_2020_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2020_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:08</t>
+    <t xml:space="preserve">2026-09-09 23:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2020_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2020_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:02</t>
+    <t xml:space="preserve">2026-09-17 13:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2020_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2020_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 13:59</t>
+    <t xml:space="preserve">2026-09-23 12:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2020_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2020_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:28</t>
+    <t xml:space="preserve">2026-10-02 13:45</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2020_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2020_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:45</t>
+    <t xml:space="preserve">2026-10-04 08:50</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2020_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2020_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:50</t>
+    <t xml:space="preserve">2026-10-05 10:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -728,7 +728,7 @@
         <v>2020</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>856824.62</v>
+        <v>856824.63</v>
       </c>
     </row>
     <row r="11">
@@ -1000,7 +1000,7 @@
         <v>2020</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>728741.62</v>
+        <v>728741.63</v>
       </c>
     </row>
     <row r="27">
@@ -1017,7 +1017,7 @@
         <v>2020</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>727542.62</v>
+        <v>727542.63</v>
       </c>
     </row>
     <row r="28">
@@ -1136,7 +1136,7 @@
         <v>2020</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>677238.12</v>
+        <v>677238.13</v>
       </c>
     </row>
     <row r="35">
@@ -1221,7 +1221,7 @@
         <v>2020</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>644159.12</v>
+        <v>644159.13</v>
       </c>
     </row>
   </sheetData>
